--- a/Lake Trends.xlsx
+++ b/Lake Trends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officemgmtentserv-my.sharepoint.com/personal/jordon_henderson_owrb_ok_gov/Documents/Documents/Factsheets_HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{AB8F8A81-B659-460C-97B1-4A36028393DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62B9281C-3D50-4C55-B12E-C49682D745D8}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{AB8F8A81-B659-460C-97B1-4A36028393DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{873F69A2-3F84-426B-BB2A-150E4C1907EC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45EE3177-148E-4463-BCC1-B47E3C070BBF}"/>
   </bookViews>

--- a/Lake Trends.xlsx
+++ b/Lake Trends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officemgmtentserv-my.sharepoint.com/personal/jordon_henderson_owrb_ok_gov/Documents/Documents/Factsheets_HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{AB8F8A81-B659-460C-97B1-4A36028393DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{873F69A2-3F84-426B-BB2A-150E4C1907EC}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{AB8F8A81-B659-460C-97B1-4A36028393DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{546F70C8-066F-4A68-8D81-963E85BC223A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45EE3177-148E-4463-BCC1-B47E3C070BBF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12897" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12897" uniqueCount="317">
   <si>
     <t>Lake</t>
   </si>
@@ -977,21 +977,6 @@
     <t>Shawnee Twin#2</t>
   </si>
   <si>
-    <t>Shawnee Twin#3</t>
-  </si>
-  <si>
-    <t>Shawnee Twin#4</t>
-  </si>
-  <si>
-    <t>Shawnee Twin#5</t>
-  </si>
-  <si>
-    <t>Shawnee Twin#6</t>
-  </si>
-  <si>
-    <t>Shawnee Twin#7</t>
-  </si>
-  <si>
     <t>Tenkiller Ferry</t>
   </si>
   <si>
@@ -28031,7 +28016,7 @@
     </row>
     <row r="458" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B458" t="s">
         <v>11</v>
@@ -28088,7 +28073,7 @@
     </row>
     <row r="459" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B459" t="s">
         <v>11</v>
@@ -28145,7 +28130,7 @@
     </row>
     <row r="460" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B460" t="s">
         <v>11</v>
@@ -28205,7 +28190,7 @@
     </row>
     <row r="461" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B461" t="s">
         <v>11</v>
@@ -28262,7 +28247,7 @@
     </row>
     <row r="462" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B462" t="s">
         <v>11</v>
@@ -28382,7 +28367,7 @@
     </row>
     <row r="464" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B464" t="s">
         <v>11</v>
@@ -28439,7 +28424,7 @@
     </row>
     <row r="465" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B465" t="s">
         <v>11</v>
@@ -28499,7 +28484,7 @@
     </row>
     <row r="466" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B466" t="s">
         <v>11</v>
@@ -28559,7 +28544,7 @@
     </row>
     <row r="467" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B467" t="s">
         <v>11</v>
@@ -28619,7 +28604,7 @@
     </row>
     <row r="468" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B468" t="s">
         <v>11</v>
@@ -31814,7 +31799,7 @@
     </row>
     <row r="523" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B523" t="s">
         <v>11</v>
@@ -31874,7 +31859,7 @@
     </row>
     <row r="524" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B524" t="s">
         <v>11</v>
@@ -31934,7 +31919,7 @@
     </row>
     <row r="525" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B525" t="s">
         <v>11</v>
@@ -31991,7 +31976,7 @@
     </row>
     <row r="526" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B526" t="s">
         <v>11</v>
@@ -32051,7 +32036,7 @@
     </row>
     <row r="527" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B527" t="s">
         <v>11</v>
@@ -32111,7 +32096,7 @@
     </row>
     <row r="528" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B528" t="s">
         <v>11</v>
@@ -32845,7 +32830,7 @@
     </row>
     <row r="541" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B541" t="s">
         <v>11</v>
@@ -32905,7 +32890,7 @@
     </row>
     <row r="542" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B542" t="s">
         <v>11</v>
@@ -32965,7 +32950,7 @@
     </row>
     <row r="543" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B543" t="s">
         <v>11</v>
@@ -33022,7 +33007,7 @@
     </row>
     <row r="544" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B544" t="s">
         <v>11</v>
@@ -33079,7 +33064,7 @@
     </row>
     <row r="545" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B545" t="s">
         <v>11</v>
@@ -33139,7 +33124,7 @@
     </row>
     <row r="546" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B546" t="s">
         <v>11</v>
@@ -33853,7 +33838,7 @@
     </row>
     <row r="559" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A559" s="5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B559" t="s">
         <v>11</v>
@@ -33913,7 +33898,7 @@
     </row>
     <row r="560" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A560" s="5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B560" t="s">
         <v>11</v>
@@ -33970,7 +33955,7 @@
     </row>
     <row r="561" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A561" s="5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B561" t="s">
         <v>11</v>
@@ -34030,7 +34015,7 @@
     </row>
     <row r="562" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A562" s="5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B562" t="s">
         <v>11</v>
@@ -34087,7 +34072,7 @@
     </row>
     <row r="563" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A563" s="5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B563" t="s">
         <v>11</v>
@@ -34144,7 +34129,7 @@
     </row>
     <row r="564" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A564" s="5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B564" t="s">
         <v>11</v>
@@ -34201,7 +34186,7 @@
     </row>
     <row r="565" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B565" t="s">
         <v>11</v>
@@ -34258,7 +34243,7 @@
     </row>
     <row r="566" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B566" t="s">
         <v>11</v>
@@ -34315,7 +34300,7 @@
     </row>
     <row r="567" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B567" t="s">
         <v>11</v>
@@ -34375,7 +34360,7 @@
     </row>
     <row r="568" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B568" t="s">
         <v>11</v>
@@ -34432,7 +34417,7 @@
     </row>
     <row r="569" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B569" t="s">
         <v>11</v>
@@ -34492,7 +34477,7 @@
     </row>
     <row r="570" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B570" t="s">
         <v>11</v>
@@ -34549,7 +34534,7 @@
     </row>
     <row r="571" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B571" t="s">
         <v>11</v>
@@ -34609,7 +34594,7 @@
     </row>
     <row r="572" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B572" t="s">
         <v>11</v>
@@ -34669,7 +34654,7 @@
     </row>
     <row r="573" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B573" t="s">
         <v>11</v>
@@ -34729,7 +34714,7 @@
     </row>
     <row r="574" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B574" t="s">
         <v>11</v>
@@ -34789,7 +34774,7 @@
     </row>
     <row r="575" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B575" t="s">
         <v>11</v>
@@ -34849,7 +34834,7 @@
     </row>
     <row r="576" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B576" t="s">
         <v>11</v>
@@ -35608,7 +35593,7 @@
     </row>
     <row r="589" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B589" t="s">
         <v>11</v>
@@ -35662,7 +35647,7 @@
     </row>
     <row r="590" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B590" t="s">
         <v>11</v>
@@ -35716,7 +35701,7 @@
     </row>
     <row r="591" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B591" t="s">
         <v>11</v>
@@ -35767,7 +35752,7 @@
     </row>
     <row r="592" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B592" t="s">
         <v>11</v>
@@ -35827,7 +35812,7 @@
     </row>
     <row r="593" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B593" t="s">
         <v>11</v>
@@ -35878,7 +35863,7 @@
     </row>
     <row r="594" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B594" t="s">
         <v>11</v>

--- a/Lake Trends.xlsx
+++ b/Lake Trends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officemgmtentserv-my.sharepoint.com/personal/jordon_henderson_owrb_ok_gov/Documents/Documents/Factsheets_HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{AB8F8A81-B659-460C-97B1-4A36028393DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{546F70C8-066F-4A68-8D81-963E85BC223A}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{AB8F8A81-B659-460C-97B1-4A36028393DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAB61BA7-7C8B-4B2D-AD0A-9AD1198CDCC7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45EE3177-148E-4463-BCC1-B47E3C070BBF}"/>
+    <workbookView xWindow="28680" yWindow="1395" windowWidth="29040" windowHeight="15720" xr2:uid="{45EE3177-148E-4463-BCC1-B47E3C070BBF}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL Info" sheetId="1" r:id="rId1"/>

--- a/Lake Trends.xlsx
+++ b/Lake Trends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officemgmtentserv-my.sharepoint.com/personal/jordon_henderson_owrb_ok_gov/Documents/Documents/Factsheets_HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{AB8F8A81-B659-460C-97B1-4A36028393DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAB61BA7-7C8B-4B2D-AD0A-9AD1198CDCC7}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{AB8F8A81-B659-460C-97B1-4A36028393DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E394DB62-44DE-4B8C-BCF1-C4A29E672C9C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1395" windowWidth="29040" windowHeight="15720" xr2:uid="{45EE3177-148E-4463-BCC1-B47E3C070BBF}"/>
+    <workbookView minimized="1" xWindow="32655" yWindow="5370" windowWidth="21600" windowHeight="11295" xr2:uid="{45EE3177-148E-4463-BCC1-B47E3C070BBF}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL Info" sheetId="1" r:id="rId1"/>
